--- a/matematicas_1ESOA/notas/E1A_eval2.xlsx
+++ b/matematicas_1ESOA/notas/E1A_eval2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac4744725179635e/Desktop/sapere_aude/matematicas_1ESOA/notas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="14_{EEB8211B-10C9-425F-8F6F-3DF40A5A382E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5630645B-BA49-43EB-A05A-2FA66DF667AF}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="14_{0D013055-73C7-4539-85B4-FA374B8C801D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="204" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="81">
   <si>
     <t>HOJA DE CÁLCULO PARA GENERAR UN ACTILLA DE EVALUACIÓN</t>
   </si>
@@ -348,6 +348,24 @@
     <t>SEGUNDA
 EVALUACIÓN
 PARCIAL</t>
+  </si>
+  <si>
+    <t>4*</t>
+  </si>
+  <si>
+    <t>6*</t>
+  </si>
+  <si>
+    <t>5*</t>
+  </si>
+  <si>
+    <t>7*</t>
+  </si>
+  <si>
+    <t>6**</t>
+  </si>
+  <si>
+    <t>7**</t>
   </si>
 </sst>
 </file>
@@ -427,7 +445,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -437,6 +455,18 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFD0CECE"/>
+        <bgColor rgb="FFCCCCFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor rgb="FFCCCCFF"/>
       </patternFill>
     </fill>
@@ -581,7 +611,7 @@
     <xf numFmtId="165" fontId="8" fillId="0" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -692,6 +722,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -699,91 +738,7 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Percent" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="15">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF808080"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF808080"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF808080"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF808080"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="5" tint="0.39994506668294322"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="3">
     <dxf>
       <fill>
         <patternFill>
@@ -1061,6 +1016,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1808,11 +1767,11 @@
       </c>
       <c r="X4" s="25">
         <f>COUNTIF(R2:R26,"&lt;3")-X3</f>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y4" s="26">
         <f>X4/SUM($X$3:$X$7)</f>
-        <v>0.2</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="5" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -1853,7 +1812,7 @@
         <v>8</v>
       </c>
       <c r="M5" s="37">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N5" s="21" t="s">
         <v>49</v>
@@ -1869,7 +1828,7 @@
       </c>
       <c r="R5" s="22">
         <f t="shared" si="0"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="S5" s="16" t="str">
         <f t="shared" si="1"/>
@@ -1881,18 +1840,18 @@
       </c>
       <c r="U5" s="24">
         <f t="shared" si="3"/>
-        <v>4.3</v>
+        <v>4.4000000000000004</v>
       </c>
       <c r="W5" s="29" t="s">
         <v>25</v>
       </c>
       <c r="X5" s="25">
         <f>COUNTIF(R2:R26,"&lt;5")-X3-X4</f>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5" s="26">
         <f>X5/SUM($X$3:$X$7)</f>
-        <v>0.12</v>
+        <v>0.08</v>
       </c>
     </row>
     <row r="6" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
@@ -2062,17 +2021,17 @@
       <c r="B8" s="25" t="s">
         <v>55</v>
       </c>
-      <c r="C8" s="38">
-        <v>6</v>
-      </c>
-      <c r="D8" s="38">
-        <v>4</v>
-      </c>
-      <c r="E8" s="38">
-        <v>5</v>
-      </c>
-      <c r="F8" s="38">
-        <v>5</v>
+      <c r="C8" s="38" t="s">
+        <v>76</v>
+      </c>
+      <c r="D8" s="38" t="s">
+        <v>75</v>
+      </c>
+      <c r="E8" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="F8" s="38" t="s">
+        <v>77</v>
       </c>
       <c r="G8" s="38">
         <v>8</v>
@@ -2092,8 +2051,8 @@
       <c r="L8" s="38">
         <v>4</v>
       </c>
-      <c r="M8" s="38">
-        <v>6</v>
+      <c r="M8" s="38" t="s">
+        <v>79</v>
       </c>
       <c r="N8" s="28" t="s">
         <v>49</v>
@@ -2109,7 +2068,7 @@
       </c>
       <c r="R8" s="15">
         <f t="shared" si="0"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8" s="16" t="str">
         <f t="shared" si="1"/>
@@ -2121,7 +2080,7 @@
       </c>
       <c r="U8" s="17">
         <f t="shared" si="3"/>
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="W8" s="30"/>
     </row>
@@ -2499,8 +2458,8 @@
       <c r="C14" s="38">
         <v>5</v>
       </c>
-      <c r="D14" s="28" t="s">
-        <v>49</v>
+      <c r="D14" s="43">
+        <v>7</v>
       </c>
       <c r="E14" s="38">
         <v>5</v>
@@ -2547,15 +2506,15 @@
       </c>
       <c r="S14" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T14" s="16">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U14" s="17">
         <f t="shared" si="3"/>
-        <v>6.666666666666667</v>
+        <v>6.7</v>
       </c>
       <c r="W14" s="40"/>
       <c r="X14" s="40"/>
@@ -2711,17 +2670,17 @@
       <c r="B17" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="C17" s="37">
-        <v>7</v>
-      </c>
-      <c r="D17" s="37">
-        <v>6</v>
-      </c>
-      <c r="E17" s="37">
-        <v>6</v>
-      </c>
-      <c r="F17" s="37">
-        <v>5</v>
+      <c r="C17" s="37" t="s">
+        <v>78</v>
+      </c>
+      <c r="D17" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="E17" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="37" t="s">
+        <v>77</v>
       </c>
       <c r="G17" s="37">
         <v>5</v>
@@ -2741,8 +2700,8 @@
       <c r="L17" s="37">
         <v>5</v>
       </c>
-      <c r="M17" s="37">
-        <v>7</v>
+      <c r="M17" s="37" t="s">
+        <v>80</v>
       </c>
       <c r="N17" s="21" t="s">
         <v>49</v>
@@ -2770,7 +2729,7 @@
       </c>
       <c r="U17" s="24">
         <f t="shared" si="3"/>
-        <v>6.1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="18" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3059,8 +3018,8 @@
       <c r="C22" s="38">
         <v>8</v>
       </c>
-      <c r="D22" s="38">
-        <v>6</v>
+      <c r="D22" s="45">
+        <v>7</v>
       </c>
       <c r="E22" s="38">
         <v>7</v>
@@ -3115,7 +3074,7 @@
       </c>
       <c r="U22" s="17">
         <f t="shared" si="3"/>
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="23" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3197,8 +3156,8 @@
       <c r="C24" s="38">
         <v>7</v>
       </c>
-      <c r="D24" s="28" t="s">
-        <v>49</v>
+      <c r="D24" s="43">
+        <v>4</v>
       </c>
       <c r="E24" s="38">
         <v>4</v>
@@ -3241,19 +3200,19 @@
       </c>
       <c r="R24" s="15">
         <f t="shared" si="0"/>
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S24" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T24" s="16">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U24" s="17">
         <f t="shared" si="3"/>
-        <v>4.666666666666667</v>
+        <v>4.5999999999999996</v>
       </c>
     </row>
     <row r="25" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3266,11 +3225,11 @@
       <c r="C25" s="37">
         <v>8</v>
       </c>
-      <c r="D25" s="21" t="s">
-        <v>49</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>49</v>
+      <c r="D25" s="44">
+        <v>5</v>
+      </c>
+      <c r="E25" s="44">
+        <v>6</v>
       </c>
       <c r="F25" s="37">
         <v>9</v>
@@ -3314,15 +3273,15 @@
       </c>
       <c r="S25" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T25" s="23">
         <f t="shared" si="2"/>
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U25" s="24">
         <f t="shared" si="3"/>
-        <v>7.5</v>
+        <v>7.1</v>
       </c>
     </row>
     <row r="26" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3338,8 +3297,8 @@
       <c r="D26" s="38">
         <v>8</v>
       </c>
-      <c r="E26" s="28" t="s">
-        <v>49</v>
+      <c r="E26" s="43">
+        <v>7</v>
       </c>
       <c r="F26" s="28" t="s">
         <v>49</v>
@@ -3383,15 +3342,15 @@
       </c>
       <c r="S26" s="16" t="str">
         <f t="shared" si="1"/>
-        <v>X</v>
+        <v/>
       </c>
       <c r="T26" s="16">
         <f t="shared" si="2"/>
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U26" s="17">
         <f t="shared" si="3"/>
-        <v>8.5555555555555554</v>
+        <v>8.4</v>
       </c>
     </row>
     <row r="27" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3440,7 +3399,7 @@
       </c>
       <c r="M27" s="31">
         <f t="shared" si="4"/>
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N27" s="31">
         <f t="shared" si="4"/>
@@ -3460,7 +3419,7 @@
       </c>
       <c r="R27" s="32">
         <f>AVERAGE(R2:R26)</f>
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="S27" s="16" t="str">
         <f>IF(T27&lt;$T$27,"X","")</f>
@@ -3472,7 +3431,7 @@
       </c>
       <c r="U27" s="17">
         <f>(SUM(C2:Q26)+(COUNTIF(C2:Q26,"10-M")*10))/(COUNTIF(C2:Q26,"10-M")+COUNT(C2:Q26)+COUNTIF(C2:Q26,"NP")+COUNTIF(C2:Q26,"NE"))</f>
-        <v>6.4775510204081632</v>
+        <v>6.5041666666666664</v>
       </c>
     </row>
     <row r="28" spans="1:21" ht="15.6" x14ac:dyDescent="0.3">
@@ -3481,11 +3440,11 @@
       </c>
       <c r="C28" s="34">
         <f t="shared" ref="C28:Q28" si="5">IF((COUNT(C2:C26)+COUNTIF(C2:C26,"10-M"))=0,"--",C27/(COUNT(C2:C26)+COUNTIF(C2:C26,"10-M")))</f>
-        <v>0.12</v>
+        <v>0.13043478260869565</v>
       </c>
       <c r="D28" s="34">
         <f t="shared" si="5"/>
-        <v>0.27272727272727271</v>
+        <v>0.2608695652173913</v>
       </c>
       <c r="E28" s="34">
         <f t="shared" si="5"/>
@@ -3493,7 +3452,7 @@
       </c>
       <c r="F28" s="34">
         <f t="shared" si="5"/>
-        <v>0.17647058823529413</v>
+        <v>0.2</v>
       </c>
       <c r="G28" s="34">
         <f t="shared" si="5"/>
@@ -3521,7 +3480,7 @@
       </c>
       <c r="M28" s="34">
         <f t="shared" si="5"/>
-        <v>0.15</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="N28" s="34">
         <f t="shared" si="5"/>
@@ -3549,16 +3508,23 @@
     <mergeCell ref="W15:Y15"/>
   </mergeCells>
   <conditionalFormatting sqref="C2:Q26">
-    <cfRule type="cellIs" dxfId="5" priority="5" operator="lessThan">
+    <cfRule type="cellIs" dxfId="2" priority="5" operator="lessThan">
       <formula>5</formula>
     </cfRule>
-    <cfRule type="expression" dxfId="4" priority="7">
+    <cfRule type="expression" dxfId="1" priority="7">
       <formula>LEN(TRIM(C2))=0</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="S2:S27">
-    <cfRule type="cellIs" dxfId="3" priority="8" operator="equal">
-      <formula>"X"</formula>
+  <conditionalFormatting sqref="C27:Q27">
+    <cfRule type="colorScale" priority="1">
+      <colorScale>
+        <cfvo type="min"/>
+        <cfvo type="percentile" val="50"/>
+        <cfvo type="max"/>
+        <color rgb="FF63BE7B"/>
+        <color rgb="FFFFEB84"/>
+        <color rgb="FFF8696B"/>
+      </colorScale>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="R2:R26">
@@ -3573,6 +3539,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
+  <conditionalFormatting sqref="S2:S27">
+    <cfRule type="cellIs" dxfId="0" priority="8" operator="equal">
+      <formula>"X"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <conditionalFormatting sqref="U2:U26">
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -3585,18 +3556,6 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C27:Q27">
-    <cfRule type="colorScale" priority="1">
-      <colorScale>
-        <cfvo type="min"/>
-        <cfvo type="percentile" val="50"/>
-        <cfvo type="max"/>
-        <color rgb="FF63BE7B"/>
-        <color rgb="FFFFEB84"/>
-        <color rgb="FFF8696B"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.51180555555555496" footer="0.51180555555555496"/>
   <pageSetup paperSize="9" firstPageNumber="0" orientation="landscape" horizontalDpi="300" verticalDpi="300"/>
 </worksheet>

--- a/matematicas_1ESOA/notas/E1A_eval2.xlsx
+++ b/matematicas_1ESOA/notas/E1A_eval2.xlsx
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="229" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="81">
   <si>
     <t>HOJA DE CÁLCULO PARA GENERAR UN ACTILLA DE EVALUACIÓN</t>
   </si>
@@ -711,6 +711,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="1" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -722,15 +731,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="3" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="5" fillId="4" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -1016,10 +1016,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1349,16 +1345,16 @@
       </c>
     </row>
     <row r="8" spans="2:9" ht="25.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B8" s="42" t="s">
+      <c r="B8" s="45" t="s">
         <v>4</v>
       </c>
-      <c r="C8" s="42"/>
-      <c r="D8" s="42"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="42"/>
-      <c r="G8" s="42"/>
-      <c r="H8" s="42"/>
-      <c r="I8" s="42"/>
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="45"/>
+      <c r="F8" s="45"/>
+      <c r="G8" s="45"/>
+      <c r="H8" s="45"/>
+      <c r="I8" s="45"/>
     </row>
     <row r="9" spans="2:9" x14ac:dyDescent="0.3">
       <c r="C9" s="2" t="s">
@@ -1376,16 +1372,16 @@
       </c>
     </row>
     <row r="15" spans="2:9" ht="27" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B15" s="42" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="42"/>
-      <c r="D15" s="42"/>
-      <c r="E15" s="42"/>
-      <c r="F15" s="42"/>
-      <c r="G15" s="42"/>
-      <c r="H15" s="42"/>
-      <c r="I15" s="42"/>
+      <c r="B15" s="45" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="45"/>
+      <c r="D15" s="45"/>
+      <c r="E15" s="45"/>
+      <c r="F15" s="45"/>
+      <c r="G15" s="45"/>
+      <c r="H15" s="45"/>
+      <c r="I15" s="45"/>
     </row>
     <row r="17" spans="2:14" x14ac:dyDescent="0.3">
       <c r="B17" s="2" t="s">
@@ -1408,16 +1404,16 @@
       </c>
     </row>
     <row r="22" spans="2:14" ht="38.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B22" s="42" t="s">
+      <c r="B22" s="45" t="s">
         <v>13</v>
       </c>
-      <c r="C22" s="42"/>
-      <c r="D22" s="42"/>
-      <c r="E22" s="42"/>
-      <c r="F22" s="42"/>
-      <c r="G22" s="42"/>
-      <c r="H22" s="42"/>
-      <c r="I22" s="42"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="45"/>
+      <c r="E22" s="45"/>
+      <c r="F22" s="45"/>
+      <c r="G22" s="45"/>
+      <c r="H22" s="45"/>
+      <c r="I22" s="45"/>
     </row>
     <row r="23" spans="2:14" x14ac:dyDescent="0.3">
       <c r="N23" s="4" t="s">
@@ -2152,11 +2148,11 @@
         <f t="shared" si="3"/>
         <v>5.0999999999999996</v>
       </c>
-      <c r="W9" s="39" t="s">
+      <c r="W9" s="42" t="s">
         <v>31</v>
       </c>
-      <c r="X9" s="39"/>
-      <c r="Y9" s="39"/>
+      <c r="X9" s="42"/>
+      <c r="Y9" s="42"/>
     </row>
     <row r="10" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="27">
@@ -2226,9 +2222,9 @@
         <f t="shared" si="3"/>
         <v>7.9</v>
       </c>
-      <c r="W10" s="39"/>
-      <c r="X10" s="39"/>
-      <c r="Y10" s="39"/>
+      <c r="W10" s="42"/>
+      <c r="X10" s="42"/>
+      <c r="Y10" s="42"/>
     </row>
     <row r="11" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="19">
@@ -2298,9 +2294,9 @@
         <f t="shared" si="3"/>
         <v>8.8000000000000007</v>
       </c>
-      <c r="W11" s="39"/>
-      <c r="X11" s="39"/>
-      <c r="Y11" s="39"/>
+      <c r="W11" s="42"/>
+      <c r="X11" s="42"/>
+      <c r="Y11" s="42"/>
     </row>
     <row r="12" spans="1:25" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="27">
@@ -2370,11 +2366,11 @@
         <f t="shared" si="3"/>
         <v>7.9</v>
       </c>
-      <c r="W12" s="40" t="s">
+      <c r="W12" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="X12" s="40"/>
-      <c r="Y12" s="40"/>
+      <c r="X12" s="43"/>
+      <c r="Y12" s="43"/>
     </row>
     <row r="13" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A13" s="19">
@@ -2444,9 +2440,9 @@
         <f t="shared" si="3"/>
         <v>4.3</v>
       </c>
-      <c r="W13" s="40"/>
-      <c r="X13" s="40"/>
-      <c r="Y13" s="40"/>
+      <c r="W13" s="43"/>
+      <c r="X13" s="43"/>
+      <c r="Y13" s="43"/>
     </row>
     <row r="14" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A14" s="27">
@@ -2458,7 +2454,7 @@
       <c r="C14" s="38">
         <v>5</v>
       </c>
-      <c r="D14" s="43">
+      <c r="D14" s="39">
         <v>7</v>
       </c>
       <c r="E14" s="38">
@@ -2516,9 +2512,9 @@
         <f t="shared" si="3"/>
         <v>6.7</v>
       </c>
-      <c r="W14" s="40"/>
-      <c r="X14" s="40"/>
-      <c r="Y14" s="40"/>
+      <c r="W14" s="43"/>
+      <c r="X14" s="43"/>
+      <c r="Y14" s="43"/>
     </row>
     <row r="15" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A15" s="19">
@@ -2588,11 +2584,11 @@
         <f t="shared" si="3"/>
         <v>6.1</v>
       </c>
-      <c r="W15" s="41" t="s">
+      <c r="W15" s="44" t="s">
         <v>30</v>
       </c>
-      <c r="X15" s="41"/>
-      <c r="Y15" s="41"/>
+      <c r="X15" s="44"/>
+      <c r="Y15" s="44"/>
     </row>
     <row r="16" spans="1:25" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A16" s="27">
@@ -3018,7 +3014,7 @@
       <c r="C22" s="38">
         <v>8</v>
       </c>
-      <c r="D22" s="45">
+      <c r="D22" s="41">
         <v>7</v>
       </c>
       <c r="E22" s="38">
@@ -3156,7 +3152,7 @@
       <c r="C24" s="38">
         <v>7</v>
       </c>
-      <c r="D24" s="43">
+      <c r="D24" s="39">
         <v>4</v>
       </c>
       <c r="E24" s="38">
@@ -3225,10 +3221,10 @@
       <c r="C25" s="37">
         <v>8</v>
       </c>
-      <c r="D25" s="44">
-        <v>5</v>
-      </c>
-      <c r="E25" s="44">
+      <c r="D25" s="40">
+        <v>5</v>
+      </c>
+      <c r="E25" s="40">
         <v>6</v>
       </c>
       <c r="F25" s="37">
@@ -3297,7 +3293,7 @@
       <c r="D26" s="38">
         <v>8</v>
       </c>
-      <c r="E26" s="43">
+      <c r="E26" s="39">
         <v>7</v>
       </c>
       <c r="F26" s="28" t="s">

--- a/matematicas_1ESOA/notas/E1A_eval2.xlsx
+++ b/matematicas_1ESOA/notas/E1A_eval2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ac4744725179635e/Desktop/sapere_aude/matematicas_1ESOA/notas/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="14_{0D013055-73C7-4539-85B4-FA374B8C801D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="1" documentId="14_{0D013055-73C7-4539-85B4-FA374B8C801D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FA1E5754-CE3B-4679-9BA3-A5BF999E59AB}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
